--- a/data/trans_bre/IP09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 39,61</t>
+          <t>-22,17; 39,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 32,25</t>
+          <t>-25,69; 35,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-45,21; 35,28</t>
+          <t>-42,62; 33,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 49,34</t>
+          <t>-17,04; 49,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,9; 391,63</t>
+          <t>-75,0; 405,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,78; 132,73</t>
+          <t>-51,96; 172,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-73,87; 135,44</t>
+          <t>-73,3; 121,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 921,48</t>
+          <t>-49,05; 701,17</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 18,49</t>
+          <t>-27,2; 16,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 27,55</t>
+          <t>-11,62; 27,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 26,15</t>
+          <t>-24,92; 28,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 44,28</t>
+          <t>-22,1; 45,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,89; 87,04</t>
+          <t>-73,28; 87,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 155,93</t>
+          <t>-33,37; 139,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 109,89</t>
+          <t>-50,13; 101,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,96; 169,8</t>
+          <t>-48,58; 170,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 55,19</t>
+          <t>-9,16; 51,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 22,6</t>
+          <t>-25,8; 21,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-50,99; 19,42</t>
+          <t>-50,48; 18,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 29,14</t>
+          <t>-28,02; 32,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 861,25</t>
+          <t>-46,21; 792,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,22; 83,2</t>
+          <t>-51,3; 77,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,15; 88,88</t>
+          <t>-76,78; 71,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-64,79; 193,61</t>
+          <t>-66,16; 222,62</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,83; -3,79</t>
+          <t>-42,71; -4,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 15,84</t>
+          <t>-27,93; 15,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 27,4</t>
+          <t>-41,02; 28,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 30,31</t>
+          <t>-16,8; 30,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-93,04; -9,6</t>
+          <t>-92,79; -2,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,64; 86,76</t>
+          <t>-73,0; 70,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,98; 68,03</t>
+          <t>-60,42; 75,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,17; 193,98</t>
+          <t>-54,26; 185,42</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 5,29</t>
+          <t>-16,19; 7,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 11,57</t>
+          <t>-9,3; 14,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 10,05</t>
+          <t>-20,76; 9,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 29,73</t>
+          <t>-6,82; 30,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 22,33</t>
+          <t>-49,43; 33,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 39,18</t>
+          <t>-24,83; 51,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,86; 26,04</t>
+          <t>-39,54; 27,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 133,41</t>
+          <t>-19,68; 143,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 39,04</t>
+          <t>-20,57; 36,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 35,04</t>
+          <t>-29,01; 33,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,62; 33,93</t>
+          <t>-43,62; 35,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 49,11</t>
+          <t>-14,55; 45,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,0; 405,74</t>
+          <t>-75,08; 313,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 172,4</t>
+          <t>-56,63; 154,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-73,3; 121,63</t>
+          <t>-76,05; 137,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,05; 701,17</t>
+          <t>-42,75; 718,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 16,88</t>
+          <t>-26,97; 19,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 27,99</t>
+          <t>-11,4; 27,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 28,49</t>
+          <t>-22,47; 25,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 45,78</t>
+          <t>-22,09; 44,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,28; 87,19</t>
+          <t>-68,65; 92,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 139,61</t>
+          <t>-32,95; 153,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 101,5</t>
+          <t>-44,21; 108,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,58; 170,58</t>
+          <t>-48,29; 194,12</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 51,94</t>
+          <t>-7,22; 52,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 21,31</t>
+          <t>-24,79; 20,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-50,48; 18,29</t>
+          <t>-50,02; 23,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 32,86</t>
+          <t>-28,51; 30,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,21; 792,07</t>
+          <t>-46,77; 889,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 77,09</t>
+          <t>-49,66; 65,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,78; 71,87</t>
+          <t>-77,59; 106,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-66,16; 222,62</t>
+          <t>-66,47; 189,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,71; -4,58</t>
+          <t>-42,62; -4,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 15,03</t>
+          <t>-27,21; 17,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 28,92</t>
+          <t>-43,49; 26,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 30,98</t>
+          <t>-17,32; 29,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-92,79; -2,04</t>
+          <t>-92,68; -11,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,0; 70,07</t>
+          <t>-69,21; 94,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 75,78</t>
+          <t>-62,26; 66,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,26; 185,42</t>
+          <t>-51,19; 205,27</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 7,57</t>
+          <t>-18,16; 6,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 14,19</t>
+          <t>-9,98; 12,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 9,82</t>
+          <t>-22,23; 10,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 30,64</t>
+          <t>-6,27; 28,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 33,17</t>
+          <t>-53,53; 28,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 51,69</t>
+          <t>-26,18; 46,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 27,42</t>
+          <t>-41,37; 26,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 143,75</t>
+          <t>-16,84; 127,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,92</t>
+          <t>14,91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 36,49</t>
+          <t>-20,57; 39,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 33,13</t>
+          <t>-28,39; 32,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 35,18</t>
+          <t>-45,21; 35,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 45,04</t>
+          <t>-11,76; 48,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,08; 313,77</t>
+          <t>-72,9; 391,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,63; 154,52</t>
+          <t>-57,78; 132,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,05; 137,67</t>
+          <t>-73,87; 135,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 718,22</t>
+          <t>-36,24; 815,51</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>-9,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>-20,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 19,5</t>
+          <t>-25,8; 18,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 27,85</t>
+          <t>-10,68; 27,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 25,86</t>
+          <t>-24,81; 26,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 44,78</t>
+          <t>-33,77; 16,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 92,16</t>
+          <t>-64,89; 87,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,95; 153,24</t>
+          <t>-29,42; 155,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,21; 108,59</t>
+          <t>-46,37; 109,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,29; 194,12</t>
+          <t>-61,76; 53,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>-5,08%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 52,0</t>
+          <t>-9,65; 55,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 20,91</t>
+          <t>-24,79; 22,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 23,4</t>
+          <t>-50,99; 19,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 30,16</t>
+          <t>-32,42; 26,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,77; 889,43</t>
+          <t>-55,4; 861,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,66; 65,06</t>
+          <t>-49,22; 83,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,59; 106,51</t>
+          <t>-79,15; 88,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-66,47; 189,39</t>
+          <t>-71,08; 192,16</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,62; -4,25</t>
+          <t>-43,83; -3,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 17,27</t>
+          <t>-28,18; 15,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,49; 26,55</t>
+          <t>-38,01; 27,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 29,37</t>
+          <t>-19,23; 27,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-92,68; -11,39</t>
+          <t>-93,04; -9,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,21; 94,46</t>
+          <t>-70,64; 86,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,26; 66,67</t>
+          <t>-59,98; 68,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,19; 205,27</t>
+          <t>-57,23; 175,31</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,18</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 6,31</t>
+          <t>-18,11; 5,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 12,91</t>
+          <t>-12,28; 11,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 10,42</t>
+          <t>-20,83; 10,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 28,67</t>
+          <t>-12,18; 16,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 28,79</t>
+          <t>-54,18; 22,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 46,77</t>
+          <t>-30,34; 39,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 26,34</t>
+          <t>-39,86; 26,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 127,28</t>
+          <t>-31,07; 71,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,48</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,34</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,91</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-11,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>6.478686413044644</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.6820598594466</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-5.342807942488259</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>14.91458215666711</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2840839294229344</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.0439377543909777</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.118267457855345</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.7453003897467373</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-20,57; 39,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-28,39; 32,25</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-45,21; 35,28</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,76; 48,17</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-72,9; 391,63</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-57,78; 132,73</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-73,87; 135,44</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-36,24; 815,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-20.57371537752405</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-28.38712052659524</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-45.20697116606664</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.75707932757045</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7290017782700232</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5778227369163019</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.7386804456032551</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3624271328075838</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>39.60663617146722</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>32.24669590336287</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>35.28456715324894</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>48.16974733935051</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>3.916338292958903</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.327253799538951</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.354368589788496</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>8.155075837753744</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-5,52</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,87</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-9,71</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-16,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-20,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-25,8; 18,49</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-10,68; 27,55</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-24,81; 26,15</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-33,77; 16,8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-64,89; 87,04</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-29,42; 155,93</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-46,37; 109,89</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-61,76; 53,22</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-5.524971137127993</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7.865203660097603</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05002785653274722</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-9.71144926716596</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1666332589000134</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2768149080819679</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.001261914722161306</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2094373720828775</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>22,51</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-15,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,58</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>130,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-3,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-32,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-5,08%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-25.79777034302001</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-10.68401223301601</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-24.80626805517337</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-33.76542847056184</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.648921779212793</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2942031876370594</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4637231047060177</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6175763096436169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,65; 55,19</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-24,79; 22,6</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-50,99; 19,42</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-32,42; 26,9</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-55,4; 861,25</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-49,22; 83,2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-79,15; 88,88</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-71,08; 192,16</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>18.49481792444843</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>27.54777133076785</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>26.14915642103635</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>16.79742705069587</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.8704143397081039</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.559284086579984</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.098911354878997</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.5321877913966214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-25,15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-6,1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-6,54</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,83</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-69,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-20,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-11,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>22.50521783723566</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.567271687270178</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-15.63790896466258</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.583436761518153</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1.303296703823256</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.03920152068096541</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3280161640043506</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.05079932472257815</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-43,83; -3,79</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-28,18; 15,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-38,01; 27,4</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-19,23; 27,86</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-93,04; -9,6</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-70,64; 86,76</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-59,98; 68,03</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-57,23; 175,31</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.646346365432017</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-24.79048961864251</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-50.99267160611586</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-32.41500135235401</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5539678984620617</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4922375171602716</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.791459084711836</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7107973195087096</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>55.19345330854547</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>22.59536524329953</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>19.42187160955123</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>26.90376918726315</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>8.612462499476024</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.8319970132455446</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.8887826193833619</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.921553603512013</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-25.15020104405724</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-6.098163415994789</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-6.544412176686149</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3.826689125480498</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.6996410154086973</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2030903660063563</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1160633953068647</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1463574833822315</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-43.82675283245948</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-28.18405996047338</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-38.01435159636637</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-19.23334815127318</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.9304344963039052</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.706377754749149</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5998327291110696</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5722781647877155</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-3.794589584047366</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>15.83656805261176</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>27.39505615583284</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>27.85516293013236</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.0959930072699134</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.867629392679236</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.6802743233600299</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.753138920578064</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-6,04</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-5,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-20,97%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-12,4%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-18,11; 5,29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-12,28; 11,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-20,83; 10,05</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-12,18; 16,65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-54,18; 22,33</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-30,34; 39,18</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-39,86; 26,04</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-31,07; 71,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-6.040741411813774</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8242902565791188</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-5.730119388064531</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.648246004663834</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2097490543700615</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.0246476801954528</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1239927707521249</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.05291615679989517</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-18.10511986856548</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-12.27504825643769</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-20.82886854121656</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-12.17984721302253</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5417869167199165</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3033766220092579</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3985723486115914</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3107259689036321</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.285040659027121</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>11.573702933456</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>10.0541918296175</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>16.65264557246027</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2232633405784972</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3918261493632707</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2603526425477261</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.7183602933250477</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
